--- a/document/교육일정.xlsx
+++ b/document/교육일정.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\instructor-och\instructor-only\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\instructor-och\human-fullstack-2\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -164,69 +164,69 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Do it!  자바 완전 정복</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>짧고 굵게 배우는 JSP 웹 프로그래밍과 스프링 프레임워크
+React.js, 스프링 부트, AWS로 배우는 웹 개발 101
+GCP (자체교재)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AWS 기반 AI 애플리케이션 개발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Docker (자체교재)
+AWS 기반 AI 애플리케이션 개발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Do it! HTML+CSS+자바스크립트 웹 표준의 정석
+자바스크립트는 모든 곳에 존재한다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MariaDB로 따라 하며 배우는  SQL 프로그래밍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다중 쓰레드 프로그래밍, 네트워크 기초, 네트워크 프로그래밍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공공데이터(여행정보 API) 기반 여행 플랫폼 시스템,
+공공데이터(유기견정보 API) 기반 애견분양 플랫폼 시스템,
+건강관리 헬스테어 앱/웹 개발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가상화 시스템, 퍼블릭/프라이빗 클라우드, AWS 클라우드 활용, 도커 컨테이너</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데이터수집, 전처리, 저장, 데이터분석 파이프라인 구축, 
+클라우드 서비스 활용 머신러닝 및 딥러닝 모델 개발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로그래밍 언어 기초</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개발 환경 구축, 자료형/변수, 연산자, 제어문, 클래스 기본, 패키지
+상속, 다형성, 추상클래스, 인터페이스, 파일 입출력, 컬렉션 프레임워크</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>React.js, 스프링 부트, AWS로 배우는 웹 개발 101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>119 출동 데이터 기반 위험 상황 예측, 
 기상청 데이터 기반 날씨 예측, 
 과거 주식 데이터 기반 미래 주식 가격 예측</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Do it!  자바 완전 정복</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>짧고 굵게 배우는 JSP 웹 프로그래밍과 스프링 프레임워크
-React.js, 스프링 부트, AWS로 배우는 웹 개발 101
-GCP (자체교재)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AWS 기반 AI 애플리케이션 개발</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Docker (자체교재)
-AWS 기반 AI 애플리케이션 개발</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Do it! HTML+CSS+자바스크립트 웹 표준의 정석
-자바스크립트는 모든 곳에 존재한다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MariaDB로 따라 하며 배우는  SQL 프로그래밍</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>다중 쓰레드 프로그래밍, 네트워크 기초, 네트워크 프로그래밍</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공공데이터(여행정보 API) 기반 여행 플랫폼 시스템,
-공공데이터(유기견정보 API) 기반 애견분양 플랫폼 시스템,
-건강관리 헬스테어 앱/웹 개발</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>가상화 시스템, 퍼블릭/프라이빗 클라우드, AWS 클라우드 활용, 도커 컨테이너</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>데이터수집, 전처리, 저장, 데이터분석 파이프라인 구축, 
-클라우드 서비스 활용 머신러닝 및 딥러닝 모델 개발</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>프로그래밍 언어 기초</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>개발 환경 구축, 자료형/변수, 연산자, 제어문, 클래스 기본, 패키지
-상속, 다형성, 추상클래스, 인터페이스, 파일 입출력, 컬렉션 프레임워크</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>React.js, 스프링 부트, AWS로 배우는 웹 개발 101</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -753,7 +753,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="45.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -770,15 +770,15 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="D6" s="2">
         <v>120</v>
@@ -787,7 +787,7 @@
         <v>6</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -795,7 +795,7 @@
         <v>16</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" s="2">
         <v>40</v>
@@ -804,7 +804,7 @@
         <v>17</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
@@ -821,7 +821,7 @@
         <v>15</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -838,7 +838,7 @@
         <v>19</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -872,7 +872,7 @@
         <v>22</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D12" s="2">
         <v>55</v>
@@ -881,7 +881,7 @@
         <v>23</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="48" customHeight="1" x14ac:dyDescent="0.3">
@@ -889,7 +889,7 @@
         <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D13" s="2">
         <v>45</v>
@@ -898,7 +898,7 @@
         <v>24</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
@@ -906,7 +906,7 @@
         <v>28</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D14" s="10">
         <v>50</v>
@@ -921,7 +921,7 @@
         <v>27</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15" s="10">
         <v>212</v>
